--- a/artfynd/A 14860-2025 artfynd.xlsx
+++ b/artfynd/A 14860-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>89458876</v>
       </c>
       <c r="B2" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428649.7356223027</v>
+        <v>428650</v>
       </c>
       <c r="R2" t="n">
-        <v>6486922.986842378</v>
+        <v>6486923</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2020-11-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-11-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89458873</v>
+        <v>89458565</v>
       </c>
       <c r="B3" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,14 +808,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rud 400 m NV om, Vg</t>
+          <t>Rud 550 m NV om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428715.9230724893</v>
+        <v>428716</v>
       </c>
       <c r="R3" t="n">
-        <v>6486993.358464041</v>
+        <v>6486993</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,24 +845,14 @@
           <t>2020-11-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-11-26</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Nyckelbiotop sk 812 - 2005</t>
+          <t>Nyckelbiotop N5331 - 1996</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102887974</v>
+        <v>106510132</v>
       </c>
       <c r="B4" t="n">
-        <v>98123</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +890,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>100067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Anderstorps Väst, Vg</t>
+          <t>Ullervad-Timmersdala, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428656</v>
+        <v>428524</v>
       </c>
       <c r="R4" t="n">
-        <v>6487042</v>
+        <v>6487127</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +958,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2005-06-10</t>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2005-06-10</t>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2K. Nära obsplatsen, mot S. EEN0050 (Calluna AB) örninventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,62 +989,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Lövhage</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102887977</v>
+        <v>102887974</v>
       </c>
       <c r="B5" t="n">
-        <v>102326</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223246</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428596</v>
+        <v>428656</v>
       </c>
       <c r="R5" t="n">
-        <v>6486999</v>
+        <v>6487042</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,64 +1111,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106510132</v>
+        <v>89458572</v>
       </c>
       <c r="B6" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100067</v>
+        <v>223246</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2K</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ullervad-Timmersdala, Vg</t>
+          <t>Rud 550 m NV om, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428524.7063443267</v>
+        <v>428667</v>
       </c>
       <c r="R6" t="n">
-        <v>6487127.459891387</v>
+        <v>6487069</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1215,27 +1176,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:49</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2K. Nära obsplatsen, mot S. EEN0050 (Calluna AB) örninventering</t>
+          <t>Nyckelbiotop N5331 - 1996</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,15 +1201,223 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102887977</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Anderstorps Väst, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>428596</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6486999</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Timmersdala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2005-06-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2005-06-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lövhage</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>89458575</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91883</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>252387</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Almrostöra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hymenochaete ulmicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Corfixen &amp; Parmasto</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rud 550 m NV om, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>428667</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6487069</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Timmersdala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Nyckelbiotop N5331 - 1996</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14860-2025 artfynd.xlsx
+++ b/artfynd/A 14860-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89458876</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89458565</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106510132</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887974</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89458572</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887977</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,8 +1453,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89458575</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>